--- a/review/review_befunde.xlsx
+++ b/review/review_befunde.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +73,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -117,6 +131,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,7 +519,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -630,9 +650,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Ergebnistext über annahmen.json/ergebnistexte angehängt; Umbau des Zweigs offen</t>
         </is>
       </c>
     </row>
@@ -697,9 +717,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Zähler nach Pflicht/Recht/Ausnahme getrennt</t>
         </is>
       </c>
     </row>
@@ -764,9 +784,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Ergebnistext über annahmen.json/ergebnistexte gesetzt</t>
         </is>
       </c>
     </row>
@@ -831,9 +851,9 @@
           <t>mittel</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Adressat in der zugeklappten Zeile</t>
         </is>
       </c>
     </row>
@@ -898,9 +918,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Rechtsstand in Kopf- und Fußzeile beider Fassungen</t>
         </is>
       </c>
     </row>
@@ -965,9 +985,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Omnibus-Hinweis im Rechtsstandsblock</t>
         </is>
       </c>
     </row>
@@ -1032,9 +1052,9 @@
           <t>niedrig</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>teilweise behoben 17.09.2026 - BNetzA und DADG genannt; Bußgeldrahmen bewusst nicht, Quellenlage uneinheitlich (ANWALT)</t>
         </is>
       </c>
     </row>
@@ -1099,9 +1119,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>behoben 17.09.2026 - Rechtshinweis in der Kopfzeile der Inverso-Fassung</t>
         </is>
       </c>
     </row>
@@ -1166,9 +1186,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>entschärft 17.09.2026 - Auslieferung nur als einzelne HTML-Datei; index.html/signum bleibt unverändert</t>
         </is>
       </c>
     </row>
@@ -1233,9 +1253,9 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>entschärft 17.09.2026 - Lieferumfang auf data-act-inverso.html beschränkt</t>
         </is>
       </c>
     </row>

--- a/review/review_befunde.xlsx
+++ b/review/review_befunde.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legende" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Befunde'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Befunde'!$A$1:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1259,8 +1259,142 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>FALSCH</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>app-inverso.js; profil-inverso.json</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>zeichneGitter (Prüfung auf modulGilt statt auf die Rolle des Blocks); anknuepfungspunkte anbieter/kunde ohne eigene Bedingung</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Art. 2 Nr. 8 (Datenverarbeitungsdienst); Kap. VI adressiert Anbieter und Kunden getrennt</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>"Als Anbieter" und "Als Kunde" zeigen beide auf Modul M-VI, dessen Startbedingung ROLLE_CLOUD_ANBIETER = Ja oder ROLLE_CLOUD_KUNDE = Ja lautet. Geprüft wurde nur diese Modulbedingung, nicht die Rolle des einzelnen Blocks. Gemessen: EIN-01 = D zeigte beide Blöcke, EIN-01 = E ebenfalls.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Ein Unternehmen, das nur Cloud-Dienste anbietet, sieht zusätzlich die Kundenstrecke (Anbieterwechsel, Parallelnutzung) als eigene Betroffenheit - und umgekehrt. Überzeichnet die Betroffenheit und verwirrt im Mandantengespräch.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Anknüpfungspunkte tragen eine eigene bedingung {variable, wert}; ankerGilt() prüft Modul und Bedingung. Build und pruefe.js brechen ab, wenn zwei Anknüpfungspunkte sich ein Modul ohne eigene Bedingung teilen.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>WESENTLICH</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>BERATER</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>behoben 18.09.2026 - D zeigt nur Anbieter, E nur Kunde, D+E beide; über 63 Rollenkombinationen geprüft</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FALSCH</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>app-inverso.js</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>zeichneAusschluesse (strenge statt dreiwertiger Auswertung der Modulstartbedingung)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Art. 2 Nr. 13 (Dateninhaber); Art. 12 Abs. 1 (Anwendungsbereich Kapitel III)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Die Ausschlussreihe wertete die Modulbedingung streng aus. Kapitel III (B2B-Bedingungen) stand dadurch vom Start an als "entfällt", obwohl es sich erst bei II-06 entscheidet. Gezählt über alle M-II-Pfade bei Rolle A: 88 von 92 erreichen II-06, 72 machen M-III anwendbar.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Der Nutzer liest "entfällt" als Feststellung und hält Kapitel III für erledigt, bevor die entscheidende Frage überhaupt gestellt wurde. Für einen Dateninhaber der gefährlichste Fehlertyp: fälschliche Beruhigung.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Karte dreistufig: erfüllbar über erreichbare Fragen -&gt; "noch nicht entschieden, entscheidet sich bei II-06" mit Sprungknopf; nicht erfüllbar wegen gesperrtem Modul -&gt; "entfällt" mit Nennung des Kapitels, das den Weg öffnet; sonst "entfällt" wie bisher. Erfüllbarkeitsprobe nötig, weil bloßes Aufzählen offener Variablen irreführt.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>WESENTLICH</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>BERATER</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>behoben 18.09.2026 - bei D+E "entfällt, Frage steht in Kapitel II"; bei A+D+E "noch nicht entschieden"; nach II-06 = A erscheint der Block</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
